--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484547_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484547_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4891</v>
+        <v>6.3459</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4976</v>
+        <v>8.5526</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0085</v>
+        <v>-2.2067</v>
       </c>
       <c r="G2" t="n">
         <v>4.3301</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0594</v>
+        <v>0.9163</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1441</v>
+        <v>0.1991</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9153</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6178</v>
+        <v>2.6448</v>
       </c>
       <c r="E3" t="n">
-        <v>4.834</v>
+        <v>3.1583</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2162</v>
+        <v>-0.5135</v>
       </c>
       <c r="G3" t="n">
         <v>2.2228</v>
@@ -688,13 +688,13 @@
         <v>2.7489</v>
       </c>
       <c r="S3" t="n">
-        <v>3.191</v>
+        <v>1.218</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3409</v>
+        <v>0.6652</v>
       </c>
       <c r="U3" t="n">
-        <v>0.85</v>
+        <v>0.5528</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6127</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.772</v>
+        <v>-0.1614</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8274</v>
+        <v>1.1158</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5993</v>
+        <v>-1.2773</v>
       </c>
       <c r="G4" t="n">
         <v>-2.2604</v>
@@ -766,13 +766,13 @@
         <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6111</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0935</v>
+        <v>0.195</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.1955</v>
       </c>
       <c r="V4" t="n">
         <v>0.6335</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8437</v>
+        <v>-0.6211</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.898</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0544</v>
+        <v>0.0296</v>
       </c>
       <c r="G5" t="n">
         <v>-1.2668</v>
@@ -844,13 +844,13 @@
         <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1266</v>
+        <v>0.096</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3854</v>
+        <v>-0.138</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2587</v>
+        <v>0.234</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9596</v>
+        <v>-0.913</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6311</v>
+        <v>-0.5349</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3286</v>
+        <v>-0.3781</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6967</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.059</v>
+        <v>0.1056</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0551</v>
+        <v>0.0411</v>
       </c>
       <c r="U6" t="n">
-        <v>0.114</v>
+        <v>0.0645</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3219</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. BALAGUER BARBA</t>
+          <t>L. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0059</v>
+        <v>-1.3111</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3922</v>
+        <v>-0.3894</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6137</v>
+        <v>-0.9217</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3712</v>
+        <v>-0.141</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1631</v>
+        <v>1.5804</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-1.7214</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.6637</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5172</v>
+        <v>1.9041</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5994</v>
+        <v>-1.2404</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5466</v>
+        <v>-0.8047</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3541</v>
+        <v>-0.3237</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1925</v>
+        <v>-0.481</v>
       </c>
       <c r="P7" t="n">
         <v>0.3665</v>
@@ -1000,28 +1000,28 @@
         <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5317</v>
+        <v>0.0315</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7157</v>
+        <v>-0.1576</v>
       </c>
       <c r="U7" t="n">
-        <v>0.184</v>
+        <v>0.1891</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.212</v>
+        <v>-1.5681</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3219</v>
+        <v>0.0208</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.5339</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. GARCIA JIMENEZ</t>
+          <t>P. BALAGUER BARBA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0119</v>
+        <v>-1.7586</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9663</v>
+        <v>-0.1448</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0456</v>
+        <v>-1.6137</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.141</v>
+        <v>0.3712</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5804</v>
+        <v>1.1631</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7214</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6637</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9041</v>
+        <v>1.5172</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2404</v>
+        <v>-0.5994</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8047</v>
+        <v>-0.5466</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3237</v>
+        <v>-0.3541</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.481</v>
+        <v>-0.1925</v>
       </c>
       <c r="P8" t="n">
         <v>0.3665</v>
@@ -1078,22 +1078,22 @@
         <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6693</v>
+        <v>-0.2843</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7345</v>
+        <v>-0.4683</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.184</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5681</v>
+        <v>-2.212</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0208</v>
+        <v>0.3219</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5889</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2787</v>
+        <v>-2.6438</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2483</v>
+        <v>-0.7125</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0304</v>
+        <v>-1.9313</v>
       </c>
       <c r="G9" t="n">
         <v>0.5511</v>
@@ -1156,13 +1156,13 @@
         <v>1.8326</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5757</v>
+        <v>0.0592</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.552</v>
+        <v>-0.0162</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0237</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3219</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.895</v>
+        <v>-5.9663</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9787</v>
+        <v>-4.0749</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9163</v>
+        <v>-1.8915</v>
       </c>
       <c r="G10" t="n">
         <v>-4.2249</v>
@@ -1234,13 +1234,13 @@
         <v>2.1991</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3091</v>
+        <v>0.2377</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2172</v>
+        <v>0.1211</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0919</v>
+        <v>0.1167</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2461</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6599</v>
+        <v>-4.384600000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0444</v>
+        <v>6.319500000000001</v>
       </c>
       <c r="F11" t="n">
         <v>-10.7042</v>
@@ -1312,13 +1312,13 @@
         <v>13.7444</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1041</v>
+        <v>2.3794</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1659999999999999</v>
+        <v>0.4414</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9378</v>
+        <v>1.9382</v>
       </c>
       <c r="V11" t="n">
         <v>-5.6492</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. MATE SEBASTIA</t>
+          <t>A. MORAL SANMARTIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5548</v>
+        <v>3.2357</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8692</v>
+        <v>2.3131</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3144</v>
+        <v>0.9226</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4716</v>
+        <v>1.1456</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2252</v>
+        <v>-0.7138</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7536</v>
+        <v>1.8594</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9295</v>
+        <v>1.8877</v>
       </c>
       <c r="K12" t="n">
-        <v>2.7211</v>
+        <v>0.4768</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2084</v>
+        <v>1.4109</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.4579</v>
+        <v>-0.7421</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4959</v>
+        <v>-1.1907</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.962</v>
+        <v>0.4486</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8326</v>
+        <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2506</v>
+        <v>-0.1506</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9397</v>
+        <v>-0.276</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6891</v>
+        <v>0.1254</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>3.157</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. MORAL SANMARTIN</t>
+          <t>J. MATE SEBASTIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2231</v>
+        <v>2.6384</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9284</v>
+        <v>3.523</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2946</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1456</v>
+        <v>0.4716</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7138</v>
+        <v>1.2252</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8594</v>
+        <v>-0.7536</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8877</v>
+        <v>2.9295</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4768</v>
+        <v>2.7211</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4109</v>
+        <v>0.2084</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7421</v>
+        <v>-2.4579</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1907</v>
+        <v>-1.4959</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4486</v>
+        <v>-0.962</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9163</v>
+        <v>1.8326</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9163</v>
+        <v>1.8326</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1633</v>
+        <v>0.3343</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6606</v>
+        <v>0.5935</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5027</v>
+        <v>-0.2593</v>
       </c>
       <c r="V13" t="n">
-        <v>3.157</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1595</v>
+        <v>1.9164</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5111</v>
+        <v>0.6986</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6484</v>
+        <v>1.2178</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0462</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6936</v>
+        <v>2.7993</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6474</v>
+        <v>-2.2695</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2163</v>
+        <v>2.145</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0496</v>
+        <v>3.9014</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1667</v>
+        <v>-1.7564</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2624</v>
+        <v>-1.6152</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7431</v>
+        <v>-1.1021</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4807</v>
+        <v>-0.5131</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5498</v>
+        <v>-0.733</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5498</v>
+        <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7109</v>
+        <v>0.2296</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6606</v>
+        <v>0.0355</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3715</v>
+        <v>0.1942</v>
       </c>
       <c r="V15" t="n">
-        <v>0.945</v>
+        <v>1.89</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9554</v>
+        <v>1.267</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.0104</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8252</v>
+        <v>1.7072</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4933</v>
+        <v>2.301</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.668</v>
+        <v>-0.5937</v>
       </c>
       <c r="G16" t="n">
         <v>0.8337</v>
@@ -1702,13 +1702,13 @@
         <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3972</v>
+        <v>0.2792</v>
       </c>
       <c r="T16" t="n">
-        <v>0.457</v>
+        <v>0.2647</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0598</v>
+        <v>0.0145</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3219</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3552</v>
+        <v>1.5868</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8364</v>
+        <v>1.6072</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5188</v>
+        <v>-0.0204</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0444</v>
+        <v>-0.0462</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6502</v>
+        <v>-0.6936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3942</v>
+        <v>0.6474</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2551</v>
+        <v>1.2163</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4118</v>
+        <v>1.0496</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8433</v>
+        <v>0.1667</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2107</v>
+        <v>-1.2624</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7615</v>
+        <v>-1.7431</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4492</v>
+        <v>0.4807</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5656</v>
+        <v>0.5498</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1722</v>
+        <v>0.1382</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3137</v>
+        <v>-0.5645</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4859</v>
+        <v>0.7027</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3219</v>
+        <v>0.945</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6439</v>
+        <v>0.9554</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3219</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.354</v>
+        <v>1.138</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3139</v>
+        <v>0.9326</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0401</v>
+        <v>0.2054</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5296999999999999</v>
+        <v>1.0444</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7993</v>
+        <v>0.6502</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.2695</v>
+        <v>0.3942</v>
       </c>
       <c r="J18" t="n">
-        <v>2.145</v>
+        <v>3.2551</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9014</v>
+        <v>2.4118</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.7564</v>
+        <v>0.8433</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6152</v>
+        <v>-2.2107</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1021</v>
+        <v>-1.7615</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5131</v>
+        <v>-0.4492</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.733</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.7489</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0158</v>
+        <v>2.5656</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3327</v>
+        <v>-0.0451</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3492</v>
+        <v>-0.2175</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0164</v>
+        <v>0.1725</v>
       </c>
       <c r="V18" t="n">
-        <v>1.89</v>
+        <v>0.3219</v>
       </c>
       <c r="W18" t="n">
-        <v>1.267</v>
+        <v>0.6439</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7056</v>
+        <v>-0.3632</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5344</v>
+        <v>-0.2459</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1712</v>
+        <v>-0.1173</v>
       </c>
       <c r="G19" t="n">
         <v>0.0317</v>
@@ -1936,13 +1936,13 @@
         <v>0.9163</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4153</v>
+        <v>-0.073</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5505</v>
+        <v>-0.2621</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1352</v>
+        <v>0.1891</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3219</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1557</v>
+        <v>-1.8118</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4404</v>
+        <v>-1.3442</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7153</v>
+        <v>-0.4676</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1656</v>
@@ -2014,13 +2014,13 @@
         <v>0.3665</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7519</v>
+        <v>-0.408</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6606</v>
+        <v>-0.5645</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.1565</v>
       </c>
       <c r="V20" t="n">
         <v>0.3115</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1188</v>
+        <v>-2.0639</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4084</v>
+        <v>0.8892</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5273</v>
+        <v>-2.9531</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3996</v>
@@ -2092,13 +2092,13 @@
         <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6642</v>
+        <v>-0.6093</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7345</v>
+        <v>-0.2537</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9297</v>
+        <v>-0.3556</v>
       </c>
       <c r="V21" t="n">
         <v>0.3115</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0324</v>
+        <v>-4.2422</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8822</v>
+        <v>-2.1707</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1501</v>
+        <v>-2.0715</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5311</v>
@@ -2170,13 +2170,13 @@
         <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3075</v>
+        <v>-0.5173</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.405</v>
+        <v>-0.6934</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0974</v>
+        <v>0.1761</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6439</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.6598</v>
+        <v>5.941899999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>10.7042</v>
+        <v>10.7044</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.0444</v>
+        <v>-4.7624</v>
       </c>
       <c r="G23" t="n">
         <v>1.114700000000001</v>
@@ -2248,13 +2248,13 @@
         <v>13.7444</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.104</v>
+        <v>-0.8219999999999998</v>
       </c>
       <c r="T23" t="n">
         <v>-1.938</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1662000000000003</v>
+        <v>1.1161</v>
       </c>
       <c r="V23" t="n">
         <v>5.649199999999999</v>
